--- a/diseases/d049/2010-2014.xlsx
+++ b/diseases/d049/2010-2014.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1220,6 +1235,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1388,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1812,6 +1847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1960,6 +2000,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2108,6 +2153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2306,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2404,6 +2459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2552,6 +2612,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2700,6 +2765,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2848,6 +2918,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2996,6 +3071,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3144,6 +3224,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3292,6 +3377,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3440,6 +3530,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3588,6 +3683,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3736,6 +3836,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3884,6 +3989,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4032,6 +4142,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4328,6 +4443,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5216,6 +5336,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5956,6 +6081,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6844,6 +6974,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7582,6 +7717,11 @@
       <c r="S48" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">

--- a/diseases/d049/2010-2014.xlsx
+++ b/diseases/d049/2010-2014.xlsx
@@ -4295,28 +4295,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -4596,28 +4610,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS27" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -4744,28 +4772,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS28" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -4892,28 +4934,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS29" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -5040,28 +5096,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS30" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -5188,28 +5258,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS31" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -5489,28 +5573,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS33" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -5637,28 +5735,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -5785,28 +5897,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -5933,28 +6059,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS36" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -6234,28 +6374,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS38" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -6382,28 +6536,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS39" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -6530,28 +6698,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -6678,28 +6860,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -6826,28 +7022,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS42" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -7127,28 +7337,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS44" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -7275,28 +7499,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS45" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -7423,28 +7661,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -7571,28 +7823,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS47" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -7872,28 +8138,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -8020,28 +8300,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -8168,28 +8462,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -8316,28 +8624,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
+        </is>
+      </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">

--- a/diseases/d049/2010-2014.xlsx
+++ b/diseases/d049/2010-2014.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -788,22 +783,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -924,11 +909,6 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -941,22 +921,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1077,11 +1047,6 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1094,22 +1059,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1230,11 +1185,6 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1247,22 +1197,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1383,11 +1323,6 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1400,22 +1335,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1536,11 +1461,6 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1553,22 +1473,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1689,11 +1599,6 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1706,22 +1611,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1842,11 +1737,6 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1859,22 +1749,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1995,11 +1875,6 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2012,22 +1887,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2148,11 +2013,6 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2165,22 +2025,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2301,11 +2151,6 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2318,22 +2163,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2454,11 +2289,6 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2471,22 +2301,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2607,11 +2427,6 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2624,22 +2439,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2760,11 +2565,6 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2777,22 +2577,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2913,11 +2703,6 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2930,22 +2715,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3066,11 +2841,6 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3083,22 +2853,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3219,11 +2979,6 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3236,22 +2991,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3372,11 +3117,6 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3389,22 +3129,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3525,11 +3255,6 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3542,22 +3267,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3678,11 +3393,6 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3695,22 +3405,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3831,11 +3531,6 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3848,22 +3543,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3984,11 +3669,6 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4001,22 +3681,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4137,11 +3807,6 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4154,22 +3819,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4452,11 +4107,6 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4469,22 +4119,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -5415,11 +5055,6 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5432,22 +5067,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -6216,11 +5841,6 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6233,22 +5853,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -7179,11 +6789,6 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7196,22 +6801,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7980,11 +7575,6 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7997,22 +7587,12 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>

--- a/diseases/d049/2010-2014.xlsx
+++ b/diseases/d049/2010-2014.xlsx
@@ -3939,17 +3939,15 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U25" t="inlineStr">
         <is>
           <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
@@ -3957,7 +3955,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -3967,12 +3965,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ25" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -3982,11 +3975,6 @@
       </c>
       <c r="AT25" t="n">
         <v>1</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4239,17 +4227,15 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
@@ -4257,7 +4243,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -4267,12 +4253,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ27" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -4282,11 +4263,6 @@
       </c>
       <c r="AT27" t="n">
         <v>1</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4401,17 +4377,15 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U28" t="inlineStr">
         <is>
           <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
@@ -4419,7 +4393,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4429,12 +4403,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ28" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -4444,11 +4413,6 @@
       </c>
       <c r="AT28" t="n">
         <v>1</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4563,17 +4527,15 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U29" t="inlineStr">
         <is>
           <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
@@ -4581,7 +4543,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4591,12 +4553,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ29" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -4606,11 +4563,6 @@
       </c>
       <c r="AT29" t="n">
         <v>1</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4725,17 +4677,15 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U30" t="inlineStr">
         <is>
           <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
@@ -4743,7 +4693,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -4753,12 +4703,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ30" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -4768,11 +4713,6 @@
       </c>
       <c r="AT30" t="n">
         <v>1</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -4887,17 +4827,15 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U31" t="inlineStr">
         <is>
           <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
@@ -4905,7 +4843,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -4915,12 +4853,7 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ31" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -4930,11 +4863,6 @@
       </c>
       <c r="AT31" t="n">
         <v>1</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5187,17 +5115,15 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U33" t="inlineStr">
         <is>
           <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
@@ -5205,7 +5131,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -5215,12 +5141,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -5230,11 +5151,6 @@
       </c>
       <c r="AT33" t="n">
         <v>1</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5349,17 +5265,15 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U34" t="inlineStr">
         <is>
           <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
@@ -5367,7 +5281,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -5377,12 +5291,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -5392,11 +5301,6 @@
       </c>
       <c r="AT34" t="n">
         <v>1</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5511,17 +5415,15 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U35" t="inlineStr">
         <is>
           <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
@@ -5529,7 +5431,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -5539,12 +5441,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
@@ -5554,11 +5451,6 @@
       </c>
       <c r="AT35" t="n">
         <v>1</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5673,17 +5565,15 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U36" t="inlineStr">
         <is>
           <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
@@ -5691,7 +5581,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5701,12 +5591,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ36" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
@@ -5716,11 +5601,6 @@
       </c>
       <c r="AT36" t="n">
         <v>1</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -5973,17 +5853,15 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U38" t="inlineStr">
         <is>
           <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
@@ -5991,7 +5869,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -6001,12 +5879,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ38" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
@@ -6016,11 +5889,6 @@
       </c>
       <c r="AT38" t="n">
         <v>1</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6135,17 +6003,15 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U39" t="inlineStr">
         <is>
           <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
@@ -6153,7 +6019,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -6163,12 +6029,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ39" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
@@ -6178,11 +6039,6 @@
       </c>
       <c r="AT39" t="n">
         <v>1</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6297,17 +6153,15 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U40" t="inlineStr">
         <is>
           <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
@@ -6315,7 +6169,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -6325,12 +6179,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ40" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr">
@@ -6340,11 +6189,6 @@
       </c>
       <c r="AT40" t="n">
         <v>1</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6459,17 +6303,15 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U41" t="inlineStr">
         <is>
           <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
@@ -6477,7 +6319,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -6487,12 +6329,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ41" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
@@ -6502,11 +6339,6 @@
       </c>
       <c r="AT41" t="n">
         <v>1</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6621,17 +6453,15 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U42" t="inlineStr">
         <is>
           <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
@@ -6639,7 +6469,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -6649,12 +6479,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ42" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
@@ -6664,11 +6489,6 @@
       </c>
       <c r="AT42" t="n">
         <v>1</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6921,17 +6741,15 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U44" t="inlineStr">
         <is>
           <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
@@ -6939,7 +6757,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -6949,12 +6767,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ44" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
@@ -6964,11 +6777,6 @@
       </c>
       <c r="AT44" t="n">
         <v>1</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7083,17 +6891,15 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U45" t="inlineStr">
         <is>
           <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
@@ -7101,7 +6907,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -7111,12 +6917,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
@@ -7126,11 +6927,6 @@
       </c>
       <c r="AT45" t="n">
         <v>1</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7245,17 +7041,15 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U46" t="inlineStr">
         <is>
           <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
@@ -7263,7 +7057,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -7273,12 +7067,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ46" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
@@ -7288,11 +7077,6 @@
       </c>
       <c r="AT46" t="n">
         <v>1</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7407,17 +7191,15 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U47" t="inlineStr">
         <is>
           <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
@@ -7425,7 +7207,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -7435,12 +7217,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ47" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
@@ -7450,11 +7227,6 @@
       </c>
       <c r="AT47" t="n">
         <v>1</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7707,17 +7479,15 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U49" t="inlineStr">
         <is>
           <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
@@ -7725,7 +7495,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -7735,12 +7505,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ49" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
@@ -7750,11 +7515,6 @@
       </c>
       <c r="AT49" t="n">
         <v>1</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -7869,17 +7629,15 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U50" t="inlineStr">
         <is>
           <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
@@ -7887,7 +7645,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -7897,12 +7655,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ50" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
@@ -7912,11 +7665,6 @@
       </c>
       <c r="AT50" t="n">
         <v>1</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8031,17 +7779,15 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U51" t="inlineStr">
         <is>
           <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
@@ -8049,7 +7795,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -8059,12 +7805,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ51" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
@@ -8074,11 +7815,6 @@
       </c>
       <c r="AT51" t="n">
         <v>1</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8193,17 +7929,15 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U52" t="inlineStr">
         <is>
           <t>HOLD_JP_165c828b0fb1b842ce8afd4aadf6</t>
@@ -8211,7 +7945,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -8221,12 +7955,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ52" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
@@ -8236,11 +7965,6 @@
       </c>
       <c r="AT52" t="n">
         <v>1</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>

--- a/diseases/d049/2010-2014.xlsx
+++ b/diseases/d049/2010-2014.xlsx
@@ -771,6 +771,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -783,12 +788,22 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -909,6 +924,11 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -921,12 +941,22 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1047,6 +1077,11 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1059,12 +1094,22 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1185,6 +1230,11 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1197,12 +1247,22 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1323,6 +1383,11 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1335,12 +1400,22 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1461,6 +1536,11 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1473,12 +1553,22 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1599,6 +1689,11 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1611,12 +1706,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1737,6 +1842,11 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1749,12 +1859,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1875,6 +1995,11 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1887,12 +2012,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2013,6 +2148,11 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2025,12 +2165,22 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2151,6 +2301,11 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2163,12 +2318,22 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2289,6 +2454,11 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2301,12 +2471,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2427,6 +2607,11 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2439,12 +2624,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2565,6 +2760,11 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2577,12 +2777,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2703,6 +2913,11 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2715,12 +2930,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -2841,6 +3066,11 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2853,12 +3083,22 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -2979,6 +3219,11 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2991,12 +3236,22 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3117,6 +3372,11 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3129,12 +3389,22 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3255,6 +3525,11 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3267,12 +3542,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3393,6 +3678,11 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3405,12 +3695,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3531,6 +3831,11 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3543,12 +3848,22 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3669,6 +3984,11 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3681,12 +4001,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -3807,6 +4137,11 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3819,12 +4154,22 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4095,6 +4440,11 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4107,12 +4457,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4983,6 +5343,11 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4995,12 +5360,22 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5721,6 +6096,11 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5733,12 +6113,22 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6609,6 +6999,11 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6621,12 +7016,22 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7347,6 +7752,11 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7359,12 +7769,22 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
